--- a/ui_runner/templates/graded_analysis_tabs_2026-06-13.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-13.xlsx
@@ -471,13 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>166</v>
+      </c>
+      <c r="G2" t="n">
+        <v>57.2</v>
       </c>
     </row>
     <row r="3">
@@ -497,13 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="G3" t="n">
+        <v>51.5</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="G4" t="n">
+        <v>52.8</v>
       </c>
     </row>
     <row r="5">
@@ -549,13 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>52.9</v>
       </c>
     </row>
     <row r="6">
@@ -575,12 +587,15 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -601,13 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48.9</v>
       </c>
     </row>
     <row r="8">
@@ -627,13 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="G8" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -653,13 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55.2</v>
       </c>
     </row>
     <row r="10">
@@ -679,13 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="G10" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -705,13 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>478</v>
+      </c>
+      <c r="G11" t="n">
+        <v>61.1</v>
       </c>
     </row>
     <row r="12">
@@ -731,13 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="G12" t="n">
+        <v>68.2</v>
       </c>
     </row>
     <row r="13">
@@ -757,13 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55.6</v>
       </c>
     </row>
     <row r="14">
@@ -783,13 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>253</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31.6</v>
       </c>
     </row>
     <row r="15">
@@ -809,13 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>393</v>
+      </c>
+      <c r="G15" t="n">
+        <v>23.1</v>
       </c>
     </row>
     <row r="16">
@@ -835,13 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>247</v>
+      </c>
+      <c r="G16" t="n">
+        <v>25.8</v>
       </c>
     </row>
     <row r="17">
@@ -861,13 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4740</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>3782</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20.2</v>
       </c>
     </row>
   </sheetData>
@@ -1057,41 +1105,71 @@
           <t>Elite</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>66.7</v>
+      </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>62.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>33.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>80</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
+      <c r="N2" t="n">
+        <v>66.7</v>
+      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>19.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>311</v>
+      </c>
+      <c r="R2" t="n">
+        <v>11.1</v>
       </c>
       <c r="S2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
+      <c r="X2" t="n">
+        <v>58.3</v>
+      </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1102,8 +1180,11 @@
       <c r="AE2" t="n">
         <v>0</v>
       </c>
+      <c r="AF2" t="n">
+        <v>68.8</v>
+      </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1112,53 +1193,95 @@
           <t>Above Avg</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>67.40000000000001</v>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="D3" t="n">
+        <v>84.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="F3" t="n">
+        <v>78.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="H3" t="n">
+        <v>73.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>37.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>34.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="N3" t="n">
+        <v>27.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="P3" t="n">
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>377</v>
+      </c>
+      <c r="R3" t="n">
+        <v>72.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="T3" t="n">
+        <v>100</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
+      <c r="X3" t="n">
+        <v>30</v>
+      </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>66.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>42.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
+      <c r="AF3" t="n">
+        <v>75</v>
+      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1167,32 +1290,59 @@
           <t>Avg</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>68.2</v>
+      </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="D4" t="n">
+        <v>54.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F4" t="n">
+        <v>46.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>44.4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>53.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>21.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="N4" t="n">
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="R4" t="n">
+        <v>38.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1200,14 +1350,23 @@
       <c r="W4" t="n">
         <v>0</v>
       </c>
+      <c r="X4" t="n">
+        <v>30.8</v>
+      </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>65.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>72.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1222,53 +1381,98 @@
           <t>Below Avg</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>94.09999999999999</v>
+      </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="D5" t="n">
+        <v>85.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="F5" t="n">
+        <v>71.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="H5" t="n">
+        <v>62.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>43.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="L5" t="n">
+        <v>41.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="P5" t="n">
+        <v>21.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="R5" t="n">
+        <v>71.40000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="T5" t="n">
+        <v>100</v>
       </c>
       <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>43.8</v>
       </c>
       <c r="AA5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1277,32 +1481,59 @@
           <t>Weak</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>76.59999999999999</v>
+      </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="D6" t="n">
+        <v>68.2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="F6" t="n">
+        <v>72.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="H6" t="n">
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>53.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="L6" t="n">
+        <v>41.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="P6" t="n">
+        <v>21.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="R6" t="n">
+        <v>52.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1310,14 +1541,23 @@
       <c r="W6" t="n">
         <v>0</v>
       </c>
+      <c r="X6" t="n">
+        <v>54.5</v>
+      </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>46</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1332,53 +1572,101 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>69</v>
+      </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>348</v>
+      </c>
+      <c r="D7" t="n">
+        <v>61.1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1230</v>
+      </c>
+      <c r="F7" t="n">
+        <v>68.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>318</v>
+      </c>
+      <c r="H7" t="n">
+        <v>55.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>370</v>
+      </c>
+      <c r="L7" t="n">
+        <v>23.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>511</v>
+      </c>
+      <c r="N7" t="n">
+        <v>25.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>333</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4740</v>
+      </c>
+      <c r="R7" t="n">
+        <v>57.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>388</v>
+      </c>
+      <c r="T7" t="n">
+        <v>52.8</v>
       </c>
       <c r="U7" t="n">
+        <v>180</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>46</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>51.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>52.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>48.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>55.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/ui_runner/templates/graded_analysis_tabs_2026-06-13.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-13.xlsx
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>52.8</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E5" t="n">
         <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>52.9</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="6">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E7" t="n">
         <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>48.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="G8" t="n">
-        <v>46</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1230</v>
+        <v>1295</v>
       </c>
       <c r="E11" t="n">
-        <v>752</v>
+        <v>785</v>
       </c>
       <c r="F11" t="n">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="G11" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E12" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12" t="n">
-        <v>68.2</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
         <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>55.6</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="E14" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F14" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="G14" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F15" t="n">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="G15" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E16" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G16" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4740</v>
+        <v>5004</v>
       </c>
       <c r="E17" t="n">
-        <v>958</v>
+        <v>1017</v>
       </c>
       <c r="F17" t="n">
-        <v>3782</v>
+        <v>3987</v>
       </c>
       <c r="G17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
     </row>
   </sheetData>
@@ -1351,10 +1351,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>30.8</v>
+        <v>21.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="Z4" t="n">
         <v>65.7</v>
@@ -1579,46 +1579,46 @@
         <v>348</v>
       </c>
       <c r="D7" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1230</v>
+        <v>1295</v>
       </c>
       <c r="F7" t="n">
-        <v>68.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="H7" t="n">
-        <v>55.6</v>
+        <v>55.8</v>
       </c>
       <c r="I7" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J7" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="K7" t="n">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="L7" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="M7" t="n">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="N7" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P7" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4740</v>
+        <v>5004</v>
       </c>
       <c r="R7" t="n">
         <v>57.2</v>
@@ -1627,10 +1627,10 @@
         <v>388</v>
       </c>
       <c r="T7" t="n">
-        <v>52.8</v>
+        <v>51.6</v>
       </c>
       <c r="U7" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1639,10 +1639,10 @@
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>46</v>
+        <v>42.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="Z7" t="n">
         <v>51.5</v>
@@ -1651,22 +1651,22 @@
         <v>134</v>
       </c>
       <c r="AB7" t="n">
-        <v>52.9</v>
+        <v>51.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AD7" t="n">
-        <v>48.9</v>
+        <v>48.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF7" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
       <c r="AG7" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
